--- a/dataset_t6_grouped/results2/G5/G5_T6758_W0045F0003T0006Z000C1N46_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G5/G5_T6758_W0045F0003T0006Z000C1N46_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>48.65550327185583</v>
+        <v>7.906519281676572</v>
       </c>
       <c r="D2" t="n">
-        <v>48.16666336523913</v>
+        <v>7.827082796851359</v>
       </c>
       <c r="E2" t="n">
-        <v>12.46373234384879</v>
+        <v>2.025356505875429</v>
       </c>
       <c r="F2" t="n">
-        <v>12.4611777651992</v>
+        <v>2.02494138684487</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>38.34281990216004</v>
+        <v>6.230708234101008</v>
       </c>
       <c r="D3" t="n">
-        <v>37.75535124855461</v>
+        <v>6.135244577890124</v>
       </c>
       <c r="E3" t="n">
-        <v>12.46373234384879</v>
+        <v>2.025356505875429</v>
       </c>
       <c r="F3" t="n">
-        <v>12.4611777651992</v>
+        <v>2.02494138684487</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>40.46959214544925</v>
+        <v>6.576308723635503</v>
       </c>
       <c r="D4" t="n">
-        <v>40.06116920861051</v>
+        <v>6.509939996399208</v>
       </c>
       <c r="E4" t="n">
-        <v>12.46373234384879</v>
+        <v>2.025356505875429</v>
       </c>
       <c r="F4" t="n">
-        <v>12.4611777651992</v>
+        <v>2.02494138684487</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>48.89392488680386</v>
+        <v>7.945262794105627</v>
       </c>
       <c r="D5" t="n">
-        <v>48.79987787388097</v>
+        <v>7.929980154505658</v>
       </c>
       <c r="E5" t="n">
-        <v>12.46373234384879</v>
+        <v>2.025356505875429</v>
       </c>
       <c r="F5" t="n">
-        <v>12.4611777651992</v>
+        <v>2.02494138684487</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>18.84773434154219</v>
+        <v>3.062756830500605</v>
       </c>
       <c r="D6" t="n">
-        <v>18.30265605915694</v>
+        <v>2.974181609613003</v>
       </c>
       <c r="E6" t="n">
-        <v>12.46373234384879</v>
+        <v>2.025356505875429</v>
       </c>
       <c r="F6" t="n">
-        <v>12.4611777651992</v>
+        <v>2.02494138684487</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>45.5520314311147</v>
+        <v>7.402205107556139</v>
       </c>
       <c r="D7" t="n">
-        <v>45.59349493261084</v>
+        <v>7.408942926549261</v>
       </c>
       <c r="E7" t="n">
-        <v>12.46373234384879</v>
+        <v>2.025356505875429</v>
       </c>
       <c r="F7" t="n">
-        <v>12.4611777651992</v>
+        <v>2.02494138684487</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>40.54207338718527</v>
+        <v>6.588086925417606</v>
       </c>
       <c r="D8" t="n">
-        <v>40.40344489569286</v>
+        <v>6.565559795550091</v>
       </c>
       <c r="E8" t="n">
-        <v>12.46373234384879</v>
+        <v>2.025356505875429</v>
       </c>
       <c r="F8" t="n">
-        <v>12.4611777651992</v>
+        <v>2.02494138684487</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>9.954743546715608</v>
+        <v>1.617645826341287</v>
       </c>
       <c r="D9" t="n">
-        <v>9.781682736708946</v>
+        <v>1.589523444715204</v>
       </c>
       <c r="E9" t="n">
-        <v>12.46373234384879</v>
+        <v>2.025356505875429</v>
       </c>
       <c r="F9" t="n">
-        <v>12.4611777651992</v>
+        <v>2.02494138684487</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>34.2692106767075</v>
+        <v>5.568746734964969</v>
       </c>
       <c r="D10" t="n">
-        <v>34.30606685398476</v>
+        <v>5.574735863772523</v>
       </c>
       <c r="E10" t="n">
-        <v>12.46373234384879</v>
+        <v>2.025356505875429</v>
       </c>
       <c r="F10" t="n">
-        <v>12.4611777651992</v>
+        <v>2.02494138684487</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -768,16 +768,16 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>22.05810677753247</v>
+        <v>3.584442351349026</v>
       </c>
       <c r="D11" t="n">
-        <v>21.92924462193351</v>
+        <v>3.563502251064195</v>
       </c>
       <c r="E11" t="n">
-        <v>12.46373234384879</v>
+        <v>2.025356505875429</v>
       </c>
       <c r="F11" t="n">
-        <v>12.4611777651992</v>
+        <v>2.02494138684487</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -800,16 +800,16 @@
         <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>7.435267703339676</v>
+        <v>1.208231001792697</v>
       </c>
       <c r="D12" t="n">
-        <v>7.821511901472737</v>
+        <v>1.27099568398932</v>
       </c>
       <c r="E12" t="n">
-        <v>12.46373234384879</v>
+        <v>2.025356505875429</v>
       </c>
       <c r="F12" t="n">
-        <v>12.4611777651992</v>
+        <v>2.02494138684487</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -832,16 +832,16 @@
         <v>12</v>
       </c>
       <c r="C13" t="n">
-        <v>31.64666250789818</v>
+        <v>5.142582657533455</v>
       </c>
       <c r="D13" t="n">
-        <v>32.0499138446376</v>
+        <v>5.20811099975361</v>
       </c>
       <c r="E13" t="n">
-        <v>12.46373234384879</v>
+        <v>2.025356505875429</v>
       </c>
       <c r="F13" t="n">
-        <v>12.4611777651992</v>
+        <v>2.02494138684487</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -864,16 +864,16 @@
         <v>13</v>
       </c>
       <c r="C14" t="n">
-        <v>6.586845791367758</v>
+        <v>1.070362441097261</v>
       </c>
       <c r="D14" t="n">
-        <v>6.895355970527894</v>
+        <v>1.120495345210783</v>
       </c>
       <c r="E14" t="n">
-        <v>12.46373234384879</v>
+        <v>2.025356505875429</v>
       </c>
       <c r="F14" t="n">
-        <v>12.4611777651992</v>
+        <v>2.02494138684487</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -896,16 +896,16 @@
         <v>14</v>
       </c>
       <c r="C15" t="n">
-        <v>25.14139572422409</v>
+        <v>4.085476805186415</v>
       </c>
       <c r="D15" t="n">
-        <v>25.75157250487432</v>
+        <v>4.184630532042077</v>
       </c>
       <c r="E15" t="n">
-        <v>12.46373234384879</v>
+        <v>2.025356505875429</v>
       </c>
       <c r="F15" t="n">
-        <v>12.4611777651992</v>
+        <v>2.02494138684487</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -928,16 +928,16 @@
         <v>15</v>
       </c>
       <c r="C16" t="n">
-        <v>20.69283724319346</v>
+        <v>3.362586052018938</v>
       </c>
       <c r="D16" t="n">
-        <v>21.03352612936184</v>
+        <v>3.417947996021298</v>
       </c>
       <c r="E16" t="n">
-        <v>12.46373234384879</v>
+        <v>2.025356505875429</v>
       </c>
       <c r="F16" t="n">
-        <v>12.4611777651992</v>
+        <v>2.02494138684487</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
@@ -960,16 +960,16 @@
         <v>16</v>
       </c>
       <c r="C17" t="n">
-        <v>43.75890678524223</v>
+        <v>7.110822352601863</v>
       </c>
       <c r="D17" t="n">
-        <v>43.81464093107517</v>
+        <v>7.119879151299715</v>
       </c>
       <c r="E17" t="n">
-        <v>12.46373234384879</v>
+        <v>2.025356505875429</v>
       </c>
       <c r="F17" t="n">
-        <v>12.4611777651992</v>
+        <v>2.02494138684487</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
@@ -992,16 +992,16 @@
         <v>17</v>
       </c>
       <c r="C18" t="n">
-        <v>30.88597719190268</v>
+        <v>5.018971293684186</v>
       </c>
       <c r="D18" t="n">
-        <v>31.27588193659115</v>
+        <v>5.082330814696062</v>
       </c>
       <c r="E18" t="n">
-        <v>12.46373234384879</v>
+        <v>2.025356505875429</v>
       </c>
       <c r="F18" t="n">
-        <v>12.4611777651992</v>
+        <v>2.02494138684487</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
@@ -1024,16 +1024,16 @@
         <v>18</v>
       </c>
       <c r="C19" t="n">
-        <v>35.9504353445049</v>
+        <v>5.841945743482047</v>
       </c>
       <c r="D19" t="n">
-        <v>35.72910246930726</v>
+        <v>5.805979151262431</v>
       </c>
       <c r="E19" t="n">
-        <v>12.46373234384879</v>
+        <v>2.025356505875429</v>
       </c>
       <c r="F19" t="n">
-        <v>12.4611777651992</v>
+        <v>2.02494138684487</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
@@ -1056,16 +1056,16 @@
         <v>19</v>
       </c>
       <c r="C20" t="n">
-        <v>32.24136232780689</v>
+        <v>5.23922137826862</v>
       </c>
       <c r="D20" t="n">
-        <v>32.27110787779245</v>
+        <v>5.244055030141273</v>
       </c>
       <c r="E20" t="n">
-        <v>12.46373234384879</v>
+        <v>2.025356505875429</v>
       </c>
       <c r="F20" t="n">
-        <v>12.4611777651992</v>
+        <v>2.02494138684487</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
@@ -1088,16 +1088,16 @@
         <v>20</v>
       </c>
       <c r="C21" t="n">
-        <v>40.86703918587902</v>
+        <v>6.640893867705341</v>
       </c>
       <c r="D21" t="n">
-        <v>40.72318611841234</v>
+        <v>6.617517744242005</v>
       </c>
       <c r="E21" t="n">
-        <v>12.46373234384879</v>
+        <v>2.025356505875429</v>
       </c>
       <c r="F21" t="n">
-        <v>12.4611777651992</v>
+        <v>2.02494138684487</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
@@ -1120,16 +1120,16 @@
         <v>21</v>
       </c>
       <c r="C22" t="n">
-        <v>29.92453281790186</v>
+        <v>4.862736582909053</v>
       </c>
       <c r="D22" t="n">
-        <v>29.09707627660367</v>
+        <v>4.728274894948097</v>
       </c>
       <c r="E22" t="n">
-        <v>12.46373234384879</v>
+        <v>2.025356505875429</v>
       </c>
       <c r="F22" t="n">
-        <v>12.4611777651992</v>
+        <v>2.02494138684487</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
@@ -1152,16 +1152,16 @@
         <v>22</v>
       </c>
       <c r="C23" t="n">
-        <v>38.67607862197394</v>
+        <v>6.284862776070766</v>
       </c>
       <c r="D23" t="n">
-        <v>39.01335889410108</v>
+        <v>6.339670820291426</v>
       </c>
       <c r="E23" t="n">
-        <v>12.46373234384879</v>
+        <v>2.025356505875429</v>
       </c>
       <c r="F23" t="n">
-        <v>12.4611777651992</v>
+        <v>2.02494138684487</v>
       </c>
       <c r="G23" t="inlineStr">
         <is>
@@ -1184,16 +1184,16 @@
         <v>23</v>
       </c>
       <c r="C24" t="n">
-        <v>16.56464154991667</v>
+        <v>2.691754251861459</v>
       </c>
       <c r="D24" t="n">
-        <v>16.19694468496699</v>
+        <v>2.632003511307137</v>
       </c>
       <c r="E24" t="n">
-        <v>12.46373234384879</v>
+        <v>2.025356505875429</v>
       </c>
       <c r="F24" t="n">
-        <v>12.4611777651992</v>
+        <v>2.02494138684487</v>
       </c>
       <c r="G24" t="inlineStr">
         <is>
@@ -1216,16 +1216,16 @@
         <v>24</v>
       </c>
       <c r="C25" t="n">
-        <v>20.50570882487064</v>
+        <v>3.332177684041479</v>
       </c>
       <c r="D25" t="n">
-        <v>19.60817020626036</v>
+        <v>3.186327658517309</v>
       </c>
       <c r="E25" t="n">
-        <v>12.46373234384879</v>
+        <v>2.025356505875429</v>
       </c>
       <c r="F25" t="n">
-        <v>12.4611777651992</v>
+        <v>2.02494138684487</v>
       </c>
       <c r="G25" t="inlineStr">
         <is>
@@ -1248,16 +1248,16 @@
         <v>25</v>
       </c>
       <c r="C26" t="n">
-        <v>13.13828587037722</v>
+        <v>2.134971453936298</v>
       </c>
       <c r="D26" t="n">
-        <v>12.23315515255097</v>
+        <v>1.987887712289532</v>
       </c>
       <c r="E26" t="n">
-        <v>12.46373234384879</v>
+        <v>2.025356505875429</v>
       </c>
       <c r="F26" t="n">
-        <v>12.4611777651992</v>
+        <v>2.02494138684487</v>
       </c>
       <c r="G26" t="inlineStr">
         <is>
@@ -1280,16 +1280,16 @@
         <v>26</v>
       </c>
       <c r="C27" t="n">
-        <v>25.06659339618713</v>
+        <v>4.073321426880408</v>
       </c>
       <c r="D27" t="n">
-        <v>25.41423231832416</v>
+        <v>4.129812751727676</v>
       </c>
       <c r="E27" t="n">
-        <v>12.46373234384879</v>
+        <v>2.025356505875429</v>
       </c>
       <c r="F27" t="n">
-        <v>12.4611777651992</v>
+        <v>2.02494138684487</v>
       </c>
       <c r="G27" t="inlineStr">
         <is>
@@ -1312,16 +1312,16 @@
         <v>27</v>
       </c>
       <c r="C28" t="n">
-        <v>11.00465995430191</v>
+        <v>1.788257242574061</v>
       </c>
       <c r="D28" t="n">
-        <v>11.46811429729638</v>
+        <v>1.863568573310662</v>
       </c>
       <c r="E28" t="n">
-        <v>12.46373234384879</v>
+        <v>2.025356505875429</v>
       </c>
       <c r="F28" t="n">
-        <v>12.4611777651992</v>
+        <v>2.02494138684487</v>
       </c>
       <c r="G28" t="inlineStr">
         <is>
@@ -1344,16 +1344,16 @@
         <v>28</v>
       </c>
       <c r="C29" t="n">
-        <v>39.94236029878014</v>
+        <v>6.490633548551774</v>
       </c>
       <c r="D29" t="n">
-        <v>40.45468243740681</v>
+        <v>6.573885896078607</v>
       </c>
       <c r="E29" t="n">
-        <v>12.46373234384879</v>
+        <v>2.025356505875429</v>
       </c>
       <c r="F29" t="n">
-        <v>12.4611777651992</v>
+        <v>2.02494138684487</v>
       </c>
       <c r="G29" t="inlineStr">
         <is>
@@ -1376,16 +1376,16 @@
         <v>29</v>
       </c>
       <c r="C30" t="n">
-        <v>36.02902481791078</v>
+        <v>5.854716532910502</v>
       </c>
       <c r="D30" t="n">
-        <v>36.65426500071556</v>
+        <v>5.956318062616279</v>
       </c>
       <c r="E30" t="n">
-        <v>12.46373234384879</v>
+        <v>2.025356505875429</v>
       </c>
       <c r="F30" t="n">
-        <v>12.4611777651992</v>
+        <v>2.02494138684487</v>
       </c>
       <c r="G30" t="inlineStr">
         <is>
